--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,494 +425,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>geometry/type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ville/Commune</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Code Postale</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Code Département</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Département</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>equipe</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nb_traversees</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coordonnees</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.185179691</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>48.838378036</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H2" t="n">
-        <v>92</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.186578897</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>48.838590867</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H3" t="n">
-        <v>92</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>48.838378036,2.185179691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.185739669</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>48.839978629</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H4" t="n">
-        <v>92</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+          <t>48.839978629,2.185739669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.182423611</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>48.841659417</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H5" t="n">
-        <v>92</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>48.841659417,2.182423611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.181674192</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>48.84110189</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H6" t="n">
-        <v>92</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>48.84110189,2.181674192</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.17958393</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>48.841306214</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H7" t="n">
-        <v>92</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>48.841306214,2.17958393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.180061491</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>48.839556692</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H8" t="n">
-        <v>92</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>48.839556692,2.180061491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -528,7 +528,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -588,7 +588,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -618,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -648,7 +648,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -678,7 +678,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ville/Commune</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>equipe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nb_traversees</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>coordonnees</t>
         </is>
@@ -483,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,23 +480,20 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>48.838590867,2.186578897</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,23 +507,20 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>48.838378036,2.185179691</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,23 +534,20 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>48.839978629,2.185739669</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,23 +561,20 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>48.841659417,2.182423611</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -617,23 +588,20 @@
       <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>48.84110189,2.181674192</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>48.838378036,2.185179691</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,23 +615,20 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>48.841306214,2.17958393</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>48.838590867,2.186578897</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,16 +642,13 @@
       <c r="D8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>48.839556692,2.180061491</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>48.839978629,2.185739669</t>
         </is>
       </c>
     </row>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -413,25 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coordonnees</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ville/Commune</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>equipe</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
@@ -439,218 +439,529 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>traversee</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>coordonnees</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
-        </is>
+      <c r="A2" t="n">
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>48.841659417,2.182423611</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
-        </is>
+      <c r="A3" t="n">
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+        </is>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>48.84110189,2.181674192</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>4</v>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+        </is>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>48.841306214,2.17958393</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
+          <t>48.838590867,2.186578897</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>48.839556692,2.180061491</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>48.838378036,2.185179691</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
       <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>48.838378036,2.185179691</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>48.838590867,2.186578897</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
-        </is>
+      <c r="A8" t="n">
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
+          <t>48.838378036,2.185179691</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>48.838378036,2.185179691</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>48.839978629,2.185739669</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>48.841659417,2.182423611</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>48.841659417,2.182423611</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48.84110189,2.181674192</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48.84110189,2.181674192</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48.84110189,2.181674192</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48.841306214,2.17958393</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48.841306214,2.17958393</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48.841306214,2.17958393</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48.839556692,2.180061491</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48.839556692,2.180061491</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48.839556692,2.180061491</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.838590867,2.186578897</t>
+          <t>48.838236962,2.182082693</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,19 +494,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.838590867,2.186578897</t>
+          <t>48.838197559,2.181077932</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.838590867,2.186578897</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.838590867,2.186578897</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Pasteur / Avenue  Joffre  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Avenue  Joffre / Avenue  Pasteur  /  Boulevard   du  Général  de  Gaulle  D907 / Avenue  Pasteur  /  Place  de  la  Gare / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Joffre / Boulevard   du  Général  de  Gaulle  D907  /  Avenue  Pasteur / Boulevard   du  Général  de  Gaulle  D907  /  Place  de  la  Gare / Place  de  la  Gare  /  Avenue  Joffre / Place  de  la  Gare  /  Avenue  Pasteur</t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,16 +569,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.838378036,2.185179691</t>
+          <t>48.8391681,2.17950444</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -594,16 +594,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.838378036,2.185179691</t>
+          <t>48.8391681,2.17950444</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.838378036,2.185179691</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.838378036,2.185179691</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boulevard   du  Général  de  Gaulle  D907  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
         <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.839978629,2.185739669</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avenue  Joffre  /  Avenue  Foch / Avenue  Joffre  /  Rue  de  Villeneuve / Rue  de  Villeneuve  /  Avenue  Foch / Rue  de  Villeneuve  /  Avenue  Joffre</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,16 +694,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.838244625,2.178574511</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue  André  Guillaume   /  Boulevard  Raymond  Poincaré  D907 / Avenue  André  Guillaume   /  Rue  Pasteur / Rue  Pasteur  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,16 +819,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -844,16 +844,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -869,19 +869,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -894,19 +894,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -919,50 +919,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>48.839556692,2.180061491</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.838236962,2.182082693</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.838197559,2.181077932</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,16 +569,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.8391681,2.17950444</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -594,16 +594,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.8391681,2.17950444</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.838244625,2.178574511</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenue  André  Guillaume   /  Boulevard  Raymond  Poincaré  D907 / Avenue  André  Guillaume   /  Rue  Pasteur / Rue  Pasteur  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.839556692,2.180061491</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.8391681,2.17950444</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.8391681,2.17950444</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,16 +819,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -844,16 +844,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -869,19 +869,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -894,19 +894,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.83818105,2.180266563</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -919,25 +919,175 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.838197559,2.181077932</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48.838197559,2.181077932</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48.838197559,2.181077932</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48.838236962,2.182082693</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48.838236962,2.182082693</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48.838236962,2.182082693</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48.838244625,2.178574511</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avenue  André  Guillaume   /  Boulevard  Raymond  Poincaré  D907 / Avenue  André  Guillaume   /  Rue  Pasteur / Rue  Pasteur  /  Boulevard  Raymond  Poincaré  D907</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.841659417,2.182423611</t>
+          <t>48.797110128,2.317333369</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
+          <t>Avenue  Louis  Pasteur  D77  /  Rue  Léo  Ferré</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.795866115,2.317152518</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,12 +519,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.795866115,2.317152518</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,12 +544,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.84110189,2.181674192</t>
+          <t>48.795866115,2.317152518</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
+          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.795866115,2.317152518</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.795366804,2.31690026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Sentier de  la  Pointe des  Buttes / Rue  des  Capucines  /  Avenue  Paul  Vaillant-Couturier  D77</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.796022267,2.318268149</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.841306214,2.17958393</t>
+          <t>48.796022267,2.318268149</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
+          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.796022267,2.318268149</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.795553089,2.314239967</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  Albert  Petit  /  Rue  des  Buttes / Rue  des  Buttes  /  Avenue  Albert  Petit / Villa  des  Iris  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.795553089,2.314239967</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  Albert  Petit  /  Rue  des  Buttes / Rue  des  Buttes  /  Avenue  Albert  Petit / Villa  des  Iris  /  Avenue  Albert  Petit</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.839556692,2.180061491</t>
+          <t>48.795492673,2.313832307</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenue  Léonce  Bucquet  /  Avenue   du   Docteur  Roux / Avenue  Léonce  Bucquet  /  Rue  Pasteur / Rue  Pasteur  /  Avenue   du   Docteur  Roux</t>
+          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.8391681,2.17950444</t>
+          <t>48.795492673,2.313832307</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
+          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.8391681,2.17950444</t>
+          <t>48.795492673,2.313832307</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avenue  Casimir  Davaine  /  Rue  Pasteur</t>
+          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,16 +819,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.793416975,2.315930231</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Passage  Marie Michel Bioret  /  Avenue  Paul  Vaillant-Couturier  D77 / Rue  des  Blains   /  Avenue  Paul  Vaillant-Couturier  D77</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -844,19 +844,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.792417159,2.315486451</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Allée  Mirabeau</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -869,19 +869,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.791651109,2.315182216</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Allée  de  l'Abbé  Grégoire</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -894,19 +894,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.83818105,2.180266563</t>
+          <t>48.785990672,2.311057073</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avenue   du   Docteur  Roux  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -919,19 +919,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.838197559,2.181077932</t>
+          <t>48.785990672,2.311057073</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -944,19 +944,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>48.838197559,2.181077932</t>
+          <t>48.785990672,2.311057073</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -969,125 +969,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48.838197559,2.181077932</t>
+          <t>48.785990672,2.311057073</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Impasse Raymond  Poincaré  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>48.838236962,2.182082693</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>48.838236962,2.182082693</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>48.838236962,2.182082693</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>48.838244625,2.178574511</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avenue  André  Guillaume   /  Boulevard  Raymond  Poincaré  D907 / Avenue  André  Guillaume   /  Rue  Pasteur / Rue  Pasteur  /  Boulevard  Raymond  Poincaré  D907</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.797110128,2.317333369</t>
+          <t>48.819591174,2.266313612</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue  Louis  Pasteur  D77  /  Rue  Léo  Ferré</t>
+          <t>Rue  de  l'Égalité  D72  /  Avenue  de  la  Paix  D72 / Rue  Pierre  Brossolette  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,16 +494,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.795866115,2.317152518</t>
+          <t>48.819332567,2.269323419</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
+          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -519,16 +519,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.795866115,2.317152518</t>
+          <t>48.819332567,2.269323419</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
+          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -544,16 +544,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.795866115,2.317152518</t>
+          <t>48.819332567,2.269323419</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
+          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -569,16 +569,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.795866115,2.317152518</t>
+          <t>48.819332567,2.269323419</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Louis  Pasteur  D77  /  Avenue  Albert  Petit / Avenue  Louis  Pasteur  D77  /  Avenue  Paul  Vaillant-Couturier  D77 / Avenue  Paul  Vaillant-Couturier  D77  /  Avenue  Albert  Petit</t>
+          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.795366804,2.31690026</t>
+          <t>48.819332567,2.269323419</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Sentier de  la  Pointe des  Buttes / Rue  des  Capucines  /  Avenue  Paul  Vaillant-Couturier  D77</t>
+          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.796022267,2.318268149</t>
+          <t>48.818678282,2.27161639</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
+          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -644,12 +644,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.796022267,2.318268149</t>
+          <t>48.818678282,2.27161639</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
+          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -669,12 +669,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.796022267,2.318268149</t>
+          <t>48.818678282,2.27161639</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Passage  Wode y / Rue  de  la  Participation  /  Avenue  Albert  Petit</t>
+          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.795553089,2.314239967</t>
+          <t>48.818391263,2.271865242</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Rue  des  Buttes / Rue  des  Buttes  /  Avenue  Albert  Petit / Villa  des  Iris  /  Avenue  Albert  Petit</t>
+          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -719,12 +719,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.795553089,2.314239967</t>
+          <t>48.818391263,2.271865242</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Rue  des  Buttes / Rue  des  Buttes  /  Avenue  Albert  Petit / Villa  des  Iris  /  Avenue  Albert  Petit</t>
+          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.795492673,2.313832307</t>
+          <t>48.818391263,2.271865242</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
+          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.795492673,2.313832307</t>
+          <t>48.817326822,2.273754306</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
+          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.795492673,2.313832307</t>
+          <t>48.817326822,2.273754306</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avenue  Albert  Petit  /  Villa  des  Iris</t>
+          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,19 +819,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.793416975,2.315930231</t>
+          <t>48.817326822,2.273754306</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Passage  Marie Michel Bioret  /  Avenue  Paul  Vaillant-Couturier  D77 / Rue  des  Blains   /  Avenue  Paul  Vaillant-Couturier  D77</t>
+          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -844,19 +844,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.792417159,2.315486451</t>
+          <t>48.817326822,2.273754306</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Allée  Mirabeau</t>
+          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -869,16 +869,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.791651109,2.315182216</t>
+          <t>48.822463268,2.268081316</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue  Paul  Vaillant-Couturier  D77  /  Allée  de  l'Abbé  Grégoire</t>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -894,19 +894,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.785990672,2.311057073</t>
+          <t>48.822463268,2.268081316</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -919,19 +919,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.785990672,2.311057073</t>
+          <t>48.822463268,2.268081316</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -944,19 +944,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>48.785990672,2.311057073</t>
+          <t>48.822463268,2.268081316</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -969,25 +969,100 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48.785990672,2.311057073</t>
+          <t>48.822463268,2.268081316</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rue   du  Général  Sarrail  /  Avenue  de  Montrouge  D77</t>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48.822463268,2.268081316</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48.822463268,2.268081316</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48.822463268,2.268081316</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_4_feuille.xlsx
+++ b/data/output/Garches_Equipe_4_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.819591174,2.266313612</t>
+          <t>48.838236962,2.182082693</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rue  de  l'Égalité  D72  /  Avenue  de  la  Paix  D72 / Rue  Pierre  Brossolette  /  Avenue  de  la  Paix  D72</t>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,19 +494,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.819332567,2.269323419</t>
+          <t>48.838236962,2.182082693</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
+          <t>Rue  de  Marnes  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.819332567,2.269323419</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.819332567,2.269323419</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.819332567,2.269323419</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.819332567,2.269323419</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rue  Pierre  Curie  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.818678282,2.27161639</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.818678282,2.27161639</t>
+          <t>48.841306214,2.17958393</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  de  Brétigny  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  Brézin / Avenue  Henri  Bergson  /  Avenue  de  Brétigny</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.818678282,2.27161639</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rue  Marius Breton  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.818391263,2.271865242</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.818391263,2.271865242</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,19 +744,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.818391263,2.271865242</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avenue  de  la  Paix  D72  /  Chemin  du  Moulin / Avenue  de  la  Paix  D72  /  Rue   du  Fort  D72A / Avenue  de  la  Paix  D72  /  Rue  Marius Breton / Chemin  du  Moulin  /  Avenue  de  la  Paix  D72 / Rue   du  Fort  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -769,19 +769,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.817326822,2.273754306</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -794,19 +794,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.817326822,2.273754306</t>
+          <t>48.84110189,2.181674192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t>Avenue  Henri  Bergson  /  Grande  Rue  / Avenue  Henri  Bergson  /  Rue  Pasteur / Rue  de  Marnes  /  Avenue  Henri  Bergson</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -819,19 +819,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.817326822,2.273754306</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -844,19 +844,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.817326822,2.273754306</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rue  Barbès  /  Avenue  de  la  Paix  D72 / Rue  Gabriel  Péri  D72A  /  Avenue  de  la  Paix  D72</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -869,200 +869,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.822463268,2.268081316</t>
+          <t>48.841659417,2.182423611</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
+          <t xml:space="preserve">Avenue  de  la  Bedoyere  /  Grande  Rue </t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>48.822463268,2.268081316</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Avenue  Bourgain  D69  /  Rue  Telles de  la  Poterie / Avenue  Victor  Cresson  D989  /  Avenue  Bourgain  D69 / Avenue  Victor  Cresson  D989  /  Boulevard  Gallieni  D69 / Avenue  Victor  Cresson  D989  /  Rue  Telles de  la  Poterie / Boulevard  Gallieni  D69  /  Avenue  Bourgain  D69 / Boulevard  Gallieni  D69  /  Avenue  Victor  Cresson  D989 / Boulevard  Gallieni  D69  /  Rue  Telles de  la  Poterie / Rue  Telles de  la  Poterie  /  Avenue  Bourgain  D69 / Rue  Telles de  la  Poterie  /  Avenue  Victor  Cresson  D989</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
